--- a/_build/utils/dm-dependencies/resources/non_dm_rules.xlsx
+++ b/_build/utils/dm-dependencies/resources/non_dm_rules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni\Corpora\GUM\github\_build\utils\dm-dependencies\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D072FC-B2EB-4390-AF8C-A042526F7CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B40118-EC64-46ED-8D90-BA2F4E1970D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{BF4EFA19-1866-4339-A4F4-33A768915554}"/>
   </bookViews>
@@ -21,6 +21,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1042,7 +1045,7 @@
     <t>(accurate|aggressive|amaze|amazing|attractive|awesome|awful|bad|beautiful|big|cathartic|cautionary|clean|clear|commendable|complicated|considerable|cool|correct|crazy|critical|cute|dark|decent|different|difficult|dreadful|easy|efficient|enough|essential|excellent|excited|exciting|false|fantastic|fine|frightful|froughtful|frustrate|fun|fundamental|funny|glad|goddamn|good|great|gross|happy|hard|heady|healthy|heartwarming|high|historic|honest|icky|ideal|important|inaccurate|incorrect|insane|interesting|large|legendary|likely|long|low|lucky|magnificent|militant|natural|necessary|needy|nice|normal|okay|peaceful|perfect|pleasant|possible|practical|pretty|proud|rare|real|realistic|reliable|remarkable|right|sad|safe|same|scared|scary|scenic|significant|simple|small|smart|solid|sorry|special|strange|strong|stun|stunned|stupid|sure|surpries|surprising|sweet|tame|tired|toxic|trash|tremendous|true|unbelievable|unlikely|unnatural|unpalatable|unprecedented|useful|valuable|versatile|violent|warm|weird|wild|wild|wonderful|worth|wrong)</t>
   </si>
   <si>
-    <t>$attrib_verb = (accept|acknowledge|add|admit|afraid|agree|announce|argue|ask|assert|assess|assume|assure|aware|believe|bet|call|care|certain|chant|check|claim|comment|complain|concern|conclude|confirm|contend|convince|cry|decide|declare|demonstrate|determine|disappoint|discover|discuss|doubt|dream|emphasize|ensure|establish|estimate|exclaim|expect|explain|express|feel|figure|find|forget|gather|glad|guarantee|guess|happy|hear|hold|hope|hypothesize|imagine|implore|imply|indicate|inform|know|learn|lie|maintain|mean|mention|mindful|mutter|note|notice|observe|pant|perceive|point|posit|pray|predict|presume|promise|propose|proud|prove|quote|quoth|re-iterate|read|realise|realize|reason|recall|recognize|recommend|reiterate|remark|remember|remind|repeat|reply|report|resent|reveal|rule|say|scream|see|shout|show|shriek|shrug|sing|snap|start|state|stunned|submit|suggest|summarize|suppose|sure|surprise|surprised|suspect|swear|tell|terrify|think|trust|tweet|understand|vlog|whisper|wish|witness|wonder|worry|write|be%like|go%say|keep%mind|bear%mind|make%sure)</t>
+    <t>$attrib_verb = (accept|acknowledge|add|admit|afraid|agree|announce|argue|ask|assert|assess|assume|assure|aware|believe|bet|call|care|certain|chant|check|claim|comment|complain|concern|conclude|confirm|consider|contend|convince|cry|decide|declare|demonstrate|determine|disappoint|discover|discuss|doubt|dream|emphasize|ensure|establish|estimate|exclaim|expect|explain|express|exult|feel|figure|find|forget|gather|glad|guarantee|guess|happy|hear|hold|hope|hypothesize|imagine|implore|imply|indicate|inform|know|learn|lie|maintain|mean|mention|mindful|mutter|note|notice|observe|pant|perceive|point|posit|pray|predict|presume|promise|propose|proud|prove|quote|quoth|re-iterate|read|realise|realize|reason|recall|recognize|recommend|reiterate|remark|remember|remind|repeat|reply|report|request|resent|reveal|rule|say|scream|see|shout|show|shriek|shrug|sing|snap|start|state|stunned|submit|suggest|summarize|suppose|sure|surprise|surprised|suspect|swear|tell|terrify|think|trust|tweet|understand|vlog|warn|whisper|wish|witness|wonder|worry|write|yell|be%like|go%say|keep%mind|bear%mind|make%sure)</t>
   </si>
 </sst>
 </file>

--- a/_build/utils/dm-dependencies/resources/non_dm_rules.xlsx
+++ b/_build/utils/dm-dependencies/resources/non_dm_rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni\Corpora\GUM\github\_build\utils\dm-dependencies\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B40118-EC64-46ED-8D90-BA2F4E1970D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5A7052-63DC-4974-B881-875D745C0E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{BF4EFA19-1866-4339-A4F4-33A768915554}"/>
   </bookViews>
@@ -904,9 +904,6 @@
     <t>(not|never)</t>
   </si>
   <si>
-    <t>(sorry|welcome|thank|sure|alright|thanks|mhm|mm|yeah|oh|well|unhunh|m-m|hi|bye|right|ok|okay|um|right|hm)</t>
-  </si>
-  <si>
     <t>(should|ought|must)</t>
   </si>
   <si>
@@ -1046,6 +1043,9 @@
   </si>
   <si>
     <t>$attrib_verb = (accept|acknowledge|add|admit|afraid|agree|announce|argue|ask|assert|assess|assume|assure|aware|believe|bet|call|care|certain|chant|check|claim|comment|complain|concern|conclude|confirm|consider|contend|convince|cry|decide|declare|demonstrate|determine|disappoint|discover|discuss|doubt|dream|emphasize|ensure|establish|estimate|exclaim|expect|explain|express|exult|feel|figure|find|forget|gather|glad|guarantee|guess|happy|hear|hold|hope|hypothesize|imagine|implore|imply|indicate|inform|know|learn|lie|maintain|mean|mention|mindful|mutter|note|notice|observe|pant|perceive|point|posit|pray|predict|presume|promise|propose|proud|prove|quote|quoth|re-iterate|read|realise|realize|reason|recall|recognize|recommend|reiterate|remark|remember|remind|repeat|reply|report|request|resent|reveal|rule|say|scream|see|shout|show|shriek|shrug|sing|snap|start|state|stunned|submit|suggest|summarize|suppose|sure|surprise|surprised|suspect|swear|tell|terrify|think|trust|tweet|understand|vlog|warn|whisper|wish|witness|wonder|worry|write|yell|be%like|go%say|keep%mind|bear%mind|make%sure)</t>
+  </si>
+  <si>
+    <t>(sorry|welcome|thank|sure|alright|thanks|mhm|mm|yeah|oh|well|unhunh|m-m|hi|bye|right|ok|okay|um|right|hm|correct)</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
@@ -1657,13 +1657,13 @@
         <v>55</v>
       </c>
       <c r="C8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
         <v>313</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>314</v>
       </c>
       <c r="F8" t="s">
         <v>88</v>
@@ -1672,7 +1672,7 @@
         <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I8" t="s">
         <v>55</v>
@@ -1705,7 +1705,7 @@
         <v>12</v>
       </c>
       <c r="S8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
@@ -1914,7 +1914,7 @@
         <v>55</v>
       </c>
       <c r="J12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K12" t="s">
         <v>55</v>
@@ -1923,7 +1923,7 @@
         <v>55</v>
       </c>
       <c r="M12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N12" t="s">
         <v>55</v>
@@ -1958,7 +1958,7 @@
         <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
@@ -1973,7 +1973,7 @@
         <v>55</v>
       </c>
       <c r="J13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -1982,7 +1982,7 @@
         <v>55</v>
       </c>
       <c r="M13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N13" t="s">
         <v>55</v>
@@ -1994,13 +1994,13 @@
         <v>13</v>
       </c>
       <c r="Q13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R13" t="s">
         <v>12</v>
       </c>
       <c r="S13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
@@ -2011,7 +2011,7 @@
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
@@ -2070,7 +2070,7 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D15" t="s">
         <v>55</v>
@@ -2129,7 +2129,7 @@
         <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D16" t="s">
         <v>55</v>
@@ -2230,7 +2230,7 @@
         <v>38</v>
       </c>
       <c r="Q17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="R17" t="s">
         <v>12</v>
@@ -2321,13 +2321,13 @@
         <v>55</v>
       </c>
       <c r="H19" t="s">
+        <v>316</v>
+      </c>
+      <c r="I19" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" t="s">
         <v>317</v>
-      </c>
-      <c r="I19" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" t="s">
-        <v>318</v>
       </c>
       <c r="K19" t="s">
         <v>55</v>
@@ -2504,10 +2504,10 @@
         <v>55</v>
       </c>
       <c r="J22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L22" t="s">
         <v>55</v>
@@ -2531,7 +2531,7 @@
         <v>12</v>
       </c>
       <c r="S22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
@@ -2539,7 +2539,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C23" t="s">
         <v>55</v>
@@ -2837,7 +2837,7 @@
         <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>291</v>
+        <v>338</v>
       </c>
       <c r="D28" t="s">
         <v>55</v>
@@ -3035,7 +3035,7 @@
         <v>55</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -3309,7 +3309,7 @@
         <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D36" t="s">
         <v>55</v>
@@ -3545,7 +3545,7 @@
         <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D40" t="s">
         <v>55</v>
@@ -3593,7 +3593,7 @@
         <v>12</v>
       </c>
       <c r="S40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.35">
@@ -4253,7 +4253,7 @@
         <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D52" t="s">
         <v>55</v>
@@ -4321,7 +4321,7 @@
         <v>55</v>
       </c>
       <c r="F53" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G53" t="s">
         <v>55</v>
@@ -4360,7 +4360,7 @@
         <v>12</v>
       </c>
       <c r="S53" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.35">
@@ -4805,7 +4805,7 @@
         <v>55</v>
       </c>
       <c r="J61" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -5513,7 +5513,7 @@
         <v>55</v>
       </c>
       <c r="J73" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K73" t="s">
         <v>55</v>
@@ -6103,7 +6103,7 @@
         <v>55</v>
       </c>
       <c r="J83" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K83" t="s">
         <v>55</v>
@@ -6495,7 +6495,7 @@
         <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D90" t="s">
         <v>55</v>
@@ -6554,7 +6554,7 @@
         <v>55</v>
       </c>
       <c r="C91" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D91" t="s">
         <v>55</v>
@@ -6731,7 +6731,7 @@
         <v>55</v>
       </c>
       <c r="C94" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D94" t="s">
         <v>55</v>
@@ -6849,7 +6849,7 @@
         <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D96" t="s">
         <v>55</v>
@@ -6908,7 +6908,7 @@
         <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D97" t="s">
         <v>55</v>
@@ -6967,7 +6967,7 @@
         <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D98" t="s">
         <v>55</v>
@@ -7085,7 +7085,7 @@
         <v>55</v>
       </c>
       <c r="C100" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D100" t="s">
         <v>55</v>
@@ -7262,7 +7262,7 @@
         <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D103" t="s">
         <v>55</v>
@@ -7292,7 +7292,7 @@
         <v>55</v>
       </c>
       <c r="M103" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N103" t="s">
         <v>55</v>
@@ -7436,7 +7436,7 @@
         <v>101</v>
       </c>
       <c r="B106" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C106" t="s">
         <v>55</v>
@@ -7731,7 +7731,7 @@
         <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C111" t="s">
         <v>55</v>
@@ -7932,7 +7932,7 @@
         <v>55</v>
       </c>
       <c r="J114" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K114" t="s">
         <v>55</v>
@@ -7991,7 +7991,7 @@
         <v>55</v>
       </c>
       <c r="J115" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K115" s="5" t="s">
         <v>55</v>
@@ -8009,16 +8009,16 @@
         <v>55</v>
       </c>
       <c r="P115" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q115" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="Q115" s="5" t="s">
-        <v>323</v>
       </c>
       <c r="R115" s="5" t="s">
         <v>12</v>
       </c>
       <c r="S115" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.35">
@@ -8050,7 +8050,7 @@
         <v>55</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K116" s="5" t="s">
         <v>55</v>
@@ -8068,16 +8068,16 @@
         <v>55</v>
       </c>
       <c r="P116" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q116" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="Q116" s="5" t="s">
-        <v>323</v>
       </c>
       <c r="R116" s="5" t="s">
         <v>12</v>
       </c>
       <c r="S116" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
